--- a/Ejercicios DAX/data/sum y sumx.xlsx
+++ b/Ejercicios DAX/data/sum y sumx.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28120"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\Desktop\A. CURSO 2024 DE POWER BI DESTOK\Módulo 04\33. SUM y SUMX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Josefina\Proyectos\Datascience\Power-BI\Ejercicios DAX\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C67D044-5788-4040-9D28-34A6202411DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5593EFA4-A9B5-47A3-834E-6FA68CB5DF14}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12144" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SUM" sheetId="2" r:id="rId1"/>
     <sheet name="SUMX" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,8 +86,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,7 +461,6 @@
         <sz val="11"/>
         <color theme="1" tint="4.9989318521683403E-2"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -561,7 +559,6 @@
         <sz val="11"/>
         <color theme="1" tint="4.9989318521683403E-2"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -701,7 +698,6 @@
         <sz val="11"/>
         <color theme="1" tint="4.9989318521683403E-2"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -736,13 +732,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB776AF4-BEFC-4747-9F33-931555F518A1}" name="Tabla1" displayName="Tabla1" ref="B2:E5" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
-  <autoFilter ref="B2:E5" xr:uid="{CB776AF4-BEFC-4747-9F33-931555F518A1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="B2:E5" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+  <autoFilter ref="B2:E5"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{90013CE1-7C4B-4537-BEF3-0F65948CF769}" name="Productos" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{5D4DFD10-049D-4E9F-A259-EB3CE855944A}" name="Unidades" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{BF28F37F-B10C-4796-99E3-C175B224F9C2}" name="Precio" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{071FEA75-74CD-4DD0-9715-A03DDE54AC1C}" name="Ventas" dataDxfId="14">
+    <tableColumn id="1" name="Productos" dataDxfId="17"/>
+    <tableColumn id="2" name="Unidades" dataDxfId="16"/>
+    <tableColumn id="3" name="Precio" dataDxfId="15"/>
+    <tableColumn id="4" name="Ventas" dataDxfId="14">
       <calculatedColumnFormula>Tabla1[[#This Row],[Unidades]]*Tabla1[[#This Row],[Precio]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -751,24 +747,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E88D7F37-E2B0-41E3-90B2-22EFA4E94AC0}" name="Tabla2" displayName="Tabla2" ref="B3:C6" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="B3:C6" xr:uid="{E88D7F37-E2B0-41E3-90B2-22EFA4E94AC0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="B3:C6" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+  <autoFilter ref="B3:C6"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8E12414C-7171-4C25-9DE6-EDA61648018E}" name="Unidades" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{888E8168-514B-4A39-A62D-B55B8D2E2055}" name="Precio" dataDxfId="8"/>
+    <tableColumn id="1" name="Unidades" dataDxfId="9"/>
+    <tableColumn id="2" name="Precio" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{45F15C9F-F2C1-4241-A574-ABED90282E6B}" name="Tabla3" displayName="Tabla3" ref="B10:E13" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
-  <autoFilter ref="B10:E13" xr:uid="{45F15C9F-F2C1-4241-A574-ABED90282E6B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="B10:E13" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="B10:E13"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{06BA2271-4B25-47E1-8FB4-9090D741D696}" name="Alumno" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{5BFC917A-80AE-4CF9-BD32-66704E976267}" name="Nota 1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{69507D53-32BF-4F81-986C-9EFEA89B879E}" name="Nota 2" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{54DC06E2-E3BA-4B38-8AAA-2CFBE8FD71C1}" name="Nota 3" dataDxfId="0"/>
+    <tableColumn id="4" name="Alumno" dataDxfId="3"/>
+    <tableColumn id="1" name="Nota 1" dataDxfId="2"/>
+    <tableColumn id="2" name="Nota 2" dataDxfId="1"/>
+    <tableColumn id="3" name="Nota 3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1090,15 +1086,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5327CE-6A92-405C-B10D-8374F3B56F09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.09765625" customWidth="1"/>
+    <col min="4" max="4" width="13.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5">
       <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
@@ -1112,22 +1108,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5">
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" s="7">
         <v>8</v>
       </c>
       <c r="E3" s="5">
         <f>Tabla1[[#This Row],[Unidades]]*Tabla1[[#This Row],[Precio]]</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
       <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
@@ -1142,7 +1138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
@@ -1157,7 +1153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="20"/>
@@ -1171,21 +1167,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAD00DC-40DA-4FE5-9861-B8CB59864ABB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" customWidth="1"/>
+    <col min="5" max="5" width="13.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:5" ht="24.6">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="18" customHeight="1">
       <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
@@ -1194,16 +1190,16 @@
       </c>
       <c r="E3" s="22"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5">
       <c r="B4" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7">
         <v>8</v>
       </c>
       <c r="E4" s="22"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" s="14">
         <v>10</v>
       </c>
@@ -1211,7 +1207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5">
       <c r="B6" s="15">
         <v>10</v>
       </c>
@@ -1219,13 +1215,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5">
       <c r="D7" s="23"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5">
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5">
       <c r="C9" s="3">
         <v>0.2</v>
       </c>
@@ -1236,7 +1232,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5">
       <c r="B10" s="19" t="s">
         <v>11</v>
       </c>
@@ -1250,7 +1246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
         <v>12</v>
       </c>
@@ -1264,7 +1260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
         <v>13</v>
       </c>
@@ -1278,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>14</v>
       </c>
@@ -1292,7 +1288,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5">
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
       <c r="E15" s="21"/>
